--- a/module4/miniproject1/planning.xlsx
+++ b/module4/miniproject1/planning.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/408a8262ffb9e406/organisedshare.ai/Institute of Data/2026-02-02-SE-FT-AP-A-B/institute-of-data-labs/module4/exercise4bmini/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/408a8262ffb9e406/organisedshare.ai/Institute of Data/2026-02-02-SE-FT-AP-A-B/institute-of-data-labs/module4/miniproject1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="516" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A989FAB1-ECED-4673-81EE-3932166E1C50}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A5371A1-62CB-460B-A798-09FC186E6666}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,7 +242,7 @@
   </si>
   <si>
     <r>
-      <t>“Research in seconds. Conviction in minutes.”</t>
+      <t>“Stock ideas move fast. Your research should too.”</t>
     </r>
     <r>
       <rPr>
@@ -252,7 +252,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 📊</t>
+      <t xml:space="preserve"> ⚡</t>
     </r>
   </si>
 </sst>
@@ -436,6 +436,211 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>531932</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>50131</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>370818</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66843</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF723B58-8613-397B-8B4B-330514FA2B46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="531932" y="1679407"/>
+          <a:ext cx="3732439" cy="2523291"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>467895</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>58487</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>306781</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>75199</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23DCE59F-1CB3-4665-A8CB-FA2B41280D1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="467895" y="5255461"/>
+          <a:ext cx="3732439" cy="2523291"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>543092</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>150395</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381978</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>167107</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B971109-04FB-4DC5-B546-467BD7B762E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="543092" y="9332829"/>
+          <a:ext cx="3732439" cy="2523291"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>409407</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>41776</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>248293</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>58488</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC88ECF0-CC5F-4B93-9574-C2858F5E8F75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="409407" y="13627434"/>
+          <a:ext cx="3732439" cy="2523291"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -638,6 +843,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -965,6 +1174,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/module4/miniproject1/planning.xlsx
+++ b/module4/miniproject1/planning.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/408a8262ffb9e406/organisedshare.ai/Institute of Data/2026-02-02-SE-FT-AP-A-B/institute-of-data-labs/module4/miniproject1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="521" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A5371A1-62CB-460B-A798-09FC186E6666}"/>
+  <xr:revisionPtr revIDLastSave="605" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E3D05BF-E5A4-44A9-BF77-1E925FCA4B25}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Landing Page" sheetId="2" r:id="rId1"/>
-    <sheet name="Share Price Chart - array" sheetId="1" r:id="rId2"/>
-    <sheet name="Share Price Chart - actual" sheetId="4" r:id="rId3"/>
-    <sheet name="Requirements" sheetId="5" r:id="rId4"/>
-    <sheet name="Add stock" sheetId="3" r:id="rId5"/>
+    <sheet name="0. Problem Solution" sheetId="6" r:id="rId1"/>
+    <sheet name="1. Requirements" sheetId="5" r:id="rId2"/>
+    <sheet name="1b. JSON objects" sheetId="1" r:id="rId3"/>
+    <sheet name="2. Landing Page" sheetId="2" r:id="rId4"/>
+    <sheet name="3. Share Price Chart - actual" sheetId="4" r:id="rId5"/>
+    <sheet name="4. Add stock" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="85">
   <si>
     <t>Share price</t>
   </si>
@@ -166,9 +167,6 @@
     <t>Unprofitable Growth</t>
   </si>
   <si>
-    <t>Landing page containing 4 lense categories</t>
-  </si>
-  <si>
     <t>https://echarts.apache.org/examples/en/editor.html?c=line-sections</t>
   </si>
   <si>
@@ -187,9 +185,6 @@
     <t>SAFE-US</t>
   </si>
   <si>
-    <t>Different data shown for each share price</t>
-  </si>
-  <si>
     <t>navbar</t>
   </si>
   <si>
@@ -205,24 +200,6 @@
     <t>add stock</t>
   </si>
   <si>
-    <t>Aim:</t>
-  </si>
-  <si>
-    <t>I want to monitor watchlist of stocks on a small mobile screen divided by lenses.</t>
-  </si>
-  <si>
-    <t>I want to see each stock's key metrics according to their lense category.</t>
-  </si>
-  <si>
-    <t>Long term the aim is to monitor stocks on a virtual holographic or VR screen so I can work on stocks anywhere, even during a meeting.</t>
-  </si>
-  <si>
-    <t>Long term I should be able to start working on a stock when friends tell me about their stock. That way I can sell my product while also save time researching things.</t>
-  </si>
-  <si>
-    <t>I want ability to add stocks quickly to watchlist and start researching it when gossiping with peers.</t>
-  </si>
-  <si>
     <t>Stock code</t>
   </si>
   <si>
@@ -230,12 +207,6 @@
   </si>
   <si>
     <t>Lenses category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long term I should add RELEVANT exchange anouncements, news articles, fund manager letters, broker reports </t>
-  </si>
-  <si>
-    <t>Stock cards page</t>
   </si>
   <si>
     <t>Stock Gossip Monitor</t>
@@ -255,12 +226,172 @@
       <t xml:space="preserve"> ⚡</t>
     </r>
   </si>
+  <si>
+    <t>1 Landing Page index.html</t>
+  </si>
+  <si>
+    <t>A mobile dashboard with large lense containers stacked vertically.</t>
+  </si>
+  <si>
+    <t>Each lense container should have a chart highlighting how lenses are doing versus the market.</t>
+  </si>
+  <si>
+    <t>2 Stock Cards Page cards.html</t>
+  </si>
+  <si>
+    <t>I want to monitor a watchlist of stocks on a small mobile screen divided by lense categories (e.g. deep value vs unprofitable growth vs profitable growth vs defensive yield).</t>
+  </si>
+  <si>
+    <t>I should be able to allocate a lense to a stock and start researching it while gossiping with my peers.</t>
+  </si>
+  <si>
+    <t>I want to see each stock's key metrics according to their lense category. I don’t want every metric for every stock.</t>
+  </si>
+  <si>
+    <t>I want to quickly add a new stock with my own name for the company and lenses category.</t>
+  </si>
+  <si>
+    <t>Then have it call on an external JSON server to populate with only the relevant metrics.</t>
+  </si>
+  <si>
+    <t>ISSUES</t>
+  </si>
+  <si>
+    <t>1. The Y axis numbers on the EChart are not to my liking, need more time to understand how it works.</t>
+  </si>
+  <si>
+    <t>2 Maybe I could have done template + dynamic cards even for landing page?</t>
+  </si>
+  <si>
+    <t>3. I wanted to have share price charts here (share price vs lense vs market), but given I couldn't even make the landing page charts work to spec, the chance of making this work are zero.</t>
+  </si>
+  <si>
+    <t>3 Add new stock addcards.html</t>
+  </si>
+  <si>
+    <t>5. Actually I want time series data for each stock calling on my API but it takes a lot of backend work.</t>
+  </si>
+  <si>
+    <t>5. The amount of internal JSON + API data manipulation I need to get this working to the extent I want is considerable, as I want to add my own data in the webpage for some properties, then afterwards fill in some other properties from my API depending on what lense I allocate it.</t>
+  </si>
+  <si>
+    <t>PROBLEM</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fundamental investment professionals cannot perform </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rigorous due diligence or monitoring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> on the move:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Due diligence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> while on the move or on a site tour, you can only really take notes on your tablet, mobile or notepad. But you need to go back to a laptop/ desktop with a larger screen to property gather materials and perform due diligence.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Monitoring:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> it is currently impossible to monitor your stocks properly (outside of share price) as research platforms provide too much information in a manner that cannot be processed in a small screen.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">“In the modern world, why should the gathering of research materials and performance of due diligence be bound by whether I have a large screen?” </t>
+  </si>
+  <si>
+    <t>SOLUTION HYPOTHESIS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“Stock ideas move fast. Your research should too.” </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I should be able to perform fundamental investment research </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>due diligence and monitoring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> on a small mobile screen.</t>
+    </r>
+  </si>
+  <si>
+    <t>When I enter the office, I should be able to seamlessly continue my work. There should be no friction between working on the move vs working at the office in front of a desktop.</t>
+  </si>
+  <si>
+    <t>Long term, I should be able to do the same type of work on a VR headset, holographic screen or VR contact lenses.</t>
+  </si>
+  <si>
+    <t>Therefore I only had 2 graphs to demonstrate I can make it work. It is run off dummy numbers.</t>
+  </si>
+  <si>
+    <t>4. No point making the frontend look nice if the backend is not presenting the raw data in the way that helps the user. Internal JSON object file.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +469,49 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -371,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -413,6 +587,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -845,10 +1052,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1111,6 +1314,466 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F6F58A5-293C-489F-AB68-C59CBFEC49EE}">
+  <dimension ref="B2:B12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="127.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="16"/>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDF7C372-B9F5-4F99-9640-73AC8C3D0BD2}">
+  <dimension ref="B1:F15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="17"/>
+    <col min="2" max="2" width="68.42578125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="17"/>
+    <col min="4" max="4" width="50" style="18" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="17"/>
+    <col min="6" max="6" width="55.140625" style="17" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D1" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B4" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B5" s="20"/>
+      <c r="D5" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="D6" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="B9" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B10" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="20"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B15" s="20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="29.85546875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D30" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3553A85-7BAF-48B3-BDA8-F22B13EECACD}">
   <dimension ref="B2:F77"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
@@ -1125,31 +1788,31 @@
   <sheetData>
     <row r="2" spans="2:6" ht="45.75" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F6" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="3:3" ht="18" x14ac:dyDescent="0.25">
@@ -1169,7 +1832,7 @@
     </row>
     <row r="77" spans="3:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C77" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1178,295 +1841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="29.85546875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E32" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDECC567-1197-4F91-930D-983B0E643FC2}">
   <dimension ref="A2:AE47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1485,7 +1860,7 @@
   <sheetData>
     <row r="2" spans="3:31" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="3:31" ht="33.75" x14ac:dyDescent="0.25">
@@ -1493,25 +1868,25 @@
         <v>38</v>
       </c>
       <c r="E3" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>53</v>
-      </c>
       <c r="L3" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE3" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="AE3" s="8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="18" x14ac:dyDescent="0.25">
@@ -1525,7 +1900,7 @@
         <v>40</v>
       </c>
       <c r="AE20" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
@@ -1780,84 +2155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDF7C372-B9F5-4F99-9640-73AC8C3D0BD2}">
-  <dimension ref="B2:L17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBEDB303-8C6A-478D-BB39-4AA40CF6AEA0}">
   <dimension ref="B2:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1867,31 +2165,31 @@
   <sheetData>
     <row r="2" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/module4/miniproject1/planning.xlsx
+++ b/module4/miniproject1/planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/408a8262ffb9e406/organisedshare.ai/Institute of Data/2026-02-02-SE-FT-AP-A-B/institute-of-data-labs/module4/miniproject1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="605" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E3D05BF-E5A4-44A9-BF77-1E925FCA4B25}"/>
+  <xr:revisionPtr revIDLastSave="610" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15AAB8A2-95AE-4B60-9079-6D731A50B45C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,9 +188,6 @@
     <t>navbar</t>
   </si>
   <si>
-    <t>ALL STOCKS</t>
-  </si>
-  <si>
     <t>home</t>
   </si>
   <si>
@@ -385,6 +382,9 @@
   </si>
   <si>
     <t>4. No point making the frontend look nice if the backend is not presenting the raw data in the way that helps the user. Internal JSON object file.</t>
+  </si>
+  <si>
+    <t>Show 1 chart at a time maybe?</t>
   </si>
 </sst>
 </file>
@@ -643,6 +643,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>41413</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4496374</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>132314</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C883F9DA-9463-9BD0-67D9-2B199AD7A97F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="993913" y="6120848"/>
+          <a:ext cx="4115374" cy="4439270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -847,7 +896,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1323,27 +1372,27 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="29.25" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="29.25" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
@@ -1351,27 +1400,27 @@
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1395,57 +1444,60 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D1" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B4" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B5" s="20"/>
       <c r="D5" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="D6" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="66" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="22"/>
@@ -1453,10 +1505,10 @@
     </row>
     <row r="11" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
@@ -1464,24 +1516,25 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1788,7 +1841,7 @@
   <sheetData>
     <row r="2" spans="2:6" ht="45.75" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
@@ -1796,18 +1849,18 @@
         <v>47</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -1859,9 +1912,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:31" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="3:31" ht="33.75" x14ac:dyDescent="0.25">
       <c r="C3" s="8" t="s">
@@ -1871,13 +1922,13 @@
         <v>47</v>
       </c>
       <c r="F3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>51</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>43</v>
@@ -2168,28 +2219,28 @@
         <v>47</v>
       </c>
       <c r="C2" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/module4/miniproject1/planning.xlsx
+++ b/module4/miniproject1/planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/408a8262ffb9e406/organisedshare.ai/Institute of Data/2026-02-02-SE-FT-AP-A-B/institute-of-data-labs/module4/miniproject1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="610" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15AAB8A2-95AE-4B60-9079-6D731A50B45C}"/>
+  <xr:revisionPtr revIDLastSave="605" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E3D05BF-E5A4-44A9-BF77-1E925FCA4B25}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,6 +188,9 @@
     <t>navbar</t>
   </si>
   <si>
+    <t>ALL STOCKS</t>
+  </si>
+  <si>
     <t>home</t>
   </si>
   <si>
@@ -382,9 +385,6 @@
   </si>
   <si>
     <t>4. No point making the frontend look nice if the backend is not presenting the raw data in the way that helps the user. Internal JSON object file.</t>
-  </si>
-  <si>
-    <t>Show 1 chart at a time maybe?</t>
   </si>
 </sst>
 </file>
@@ -643,55 +643,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>41413</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>4496374</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>132314</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C883F9DA-9463-9BD0-67D9-2B199AD7A97F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="993913" y="6120848"/>
-          <a:ext cx="4115374" cy="4439270"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -896,7 +847,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1372,27 +1323,27 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="29.25" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="29.25" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
@@ -1400,27 +1351,27 @@
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1444,60 +1395,57 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D1" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B4" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B5" s="20"/>
       <c r="D5" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="D6" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="66" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="22"/>
@@ -1505,10 +1453,10 @@
     </row>
     <row r="11" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
@@ -1516,25 +1464,24 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1841,7 +1788,7 @@
   <sheetData>
     <row r="2" spans="2:6" ht="45.75" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
@@ -1849,18 +1796,18 @@
         <v>47</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -1912,7 +1859,9 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:31" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="11"/>
+      <c r="E2" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="3" spans="3:31" ht="33.75" x14ac:dyDescent="0.25">
       <c r="C3" s="8" t="s">
@@ -1922,13 +1871,13 @@
         <v>47</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>43</v>
@@ -2219,28 +2168,28 @@
         <v>47</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
